--- a/salidas/empresas/C.xlsx
+++ b/salidas/empresas/C.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>295.5328979492188</v>
+        <v>295.5328369140625</v>
       </c>
       <c r="C2" t="n">
         <v>465.7999877929688</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>297.3454284667969</v>
+        <v>297.3451232910156</v>
       </c>
       <c r="C3" t="n">
         <v>463.7000122070312</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>302.8599853515625</v>
+        <v>302.8600158691406</v>
       </c>
       <c r="C4" t="n">
         <v>472.2999877929688</v>
@@ -539,7 +551,7 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>319.4114685058594</v>
+        <v>319.4114074707031</v>
       </c>
       <c r="C6" t="n">
         <v>493</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>312.6085205078125</v>
+        <v>312.608642578125</v>
       </c>
       <c r="C7" t="n">
         <v>482.5</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>312.9973449707031</v>
+        <v>312.997314453125</v>
       </c>
       <c r="C8" t="n">
         <v>483.1000061035156</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>322.9837341308594</v>
+        <v>322.9836730957031</v>
       </c>
       <c r="C9" t="n">
         <v>493.5</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>325.0780944824219</v>
+        <v>325.0781860351562</v>
       </c>
       <c r="C10" t="n">
         <v>496.7000122070312</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>328.2850341796875</v>
+        <v>328.2850952148438</v>
       </c>
       <c r="C11" t="n">
         <v>501.6000061035156</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>327.7610168457031</v>
+        <v>327.7607421875</v>
       </c>
       <c r="C12" t="n">
         <v>495.8999938964844</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>368.1444396972656</v>
+        <v>368.1444702148438</v>
       </c>
       <c r="C13" t="n">
         <v>557</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>364.3770751953125</v>
+        <v>364.3768310546875</v>
       </c>
       <c r="C14" t="n">
         <v>551.2999877929688</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>336.2093505859375</v>
+        <v>336.2093811035156</v>
       </c>
       <c r="C15" t="n">
         <v>503.7000122070312</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>342.6838989257812</v>
+        <v>342.6838684082031</v>
       </c>
       <c r="C16" t="n">
         <v>513.4000244140625</v>
@@ -767,7 +779,7 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>367.3628845214844</v>
+        <v>367.3629150390625</v>
       </c>
       <c r="C18" t="n">
         <v>544.9000244140625</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>345.7890014648438</v>
+        <v>345.7888488769531</v>
       </c>
       <c r="C19" t="n">
         <v>512.9000244140625</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>313.9674072265625</v>
+        <v>313.9673461914062</v>
       </c>
       <c r="C20" t="n">
         <v>465.7000122070312</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>319.7427368164062</v>
+        <v>319.7428283691406</v>
       </c>
       <c r="C21" t="n">
         <v>468.7999877929688</v>
@@ -862,7 +874,7 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
@@ -881,7 +893,7 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>230.0864715576172</v>
+        <v>230.08642578125</v>
       </c>
       <c r="C24" t="n">
         <v>333</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>203.4157867431641</v>
+        <v>203.4156799316406</v>
       </c>
       <c r="C25" t="n">
         <v>294.3999938964844</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>196.9006652832031</v>
+        <v>196.9006500244141</v>
       </c>
       <c r="C26" t="n">
         <v>281.7000122070312</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>165.7264099121094</v>
+        <v>165.7264556884766</v>
       </c>
       <c r="C27" t="n">
         <v>237.1000061035156</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>149.7199859619141</v>
+        <v>149.7200164794922</v>
       </c>
       <c r="C28" t="n">
         <v>214.1999969482422</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>176.6303405761719</v>
+        <v>176.6304321289062</v>
       </c>
       <c r="C29" t="n">
         <v>252.6999969482422</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>154.9675598144531</v>
+        <v>154.9674835205078</v>
       </c>
       <c r="C30" t="n">
         <v>218.8999938964844</v>
@@ -1033,7 +1045,7 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
@@ -1052,7 +1064,7 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>136.7639770507812</v>
+        <v>136.7640228271484</v>
       </c>
       <c r="C33" t="n">
         <v>189.8999938964844</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>147.7108612060547</v>
+        <v>147.7108764648438</v>
       </c>
       <c r="C34" t="n">
         <v>205.1000061035156</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>99.53953552246094</v>
+        <v>99.53952789306641</v>
       </c>
       <c r="C35" t="n">
         <v>136.5</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>60.45294952392578</v>
+        <v>60.45294570922852</v>
       </c>
       <c r="C36" t="n">
         <v>82.90000152587891</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>48.93114852905273</v>
+        <v>48.9311408996582</v>
       </c>
       <c r="C37" t="n">
         <v>67.09999847412109</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>25.94919204711914</v>
+        <v>25.94921493530273</v>
       </c>
       <c r="C38" t="n">
         <v>35.5</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>10.96445083618164</v>
+        <v>10.96445465087891</v>
       </c>
       <c r="C39" t="n">
         <v>15</v>
@@ -1204,7 +1216,7 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>22.29439163208008</v>
+        <v>22.29438400268555</v>
       </c>
       <c r="C41" t="n">
         <v>30.5</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>27.19184303283691</v>
+        <v>27.19184112548828</v>
       </c>
       <c r="C42" t="n">
         <v>37.20000076293945</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>21.70962333679199</v>
+        <v>21.70962142944336</v>
       </c>
       <c r="C43" t="n">
         <v>29.70000076293945</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>23.17154502868652</v>
+        <v>23.17154693603516</v>
       </c>
       <c r="C44" t="n">
         <v>31.70000076293945</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>36.54817581176758</v>
+        <v>36.54817199707031</v>
       </c>
       <c r="C45" t="n">
         <v>50</v>
@@ -1318,11 +1330,11 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>35.37863159179688</v>
+        <v>35.37864685058594</v>
       </c>
       <c r="C46" t="n">
         <v>48.40000152587891</v>
@@ -1337,11 +1349,11 @@
       <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>29.89640617370605</v>
+        <v>29.89641571044922</v>
       </c>
       <c r="C47" t="n">
         <v>40.90000152587891</v>
@@ -1356,11 +1368,11 @@
       <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>30.04260444641113</v>
+        <v>30.0425910949707</v>
       </c>
       <c r="C48" t="n">
         <v>41.09999847412109</v>
@@ -1381,7 +1393,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
@@ -1406,11 +1418,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>24.26798629760742</v>
+        <v>24.26799392700195</v>
       </c>
       <c r="C50" t="n">
         <v>33.20000076293945</v>
@@ -1431,11 +1443,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>24.85275840759277</v>
+        <v>24.85276222229004</v>
       </c>
       <c r="C51" t="n">
         <v>34</v>
@@ -1456,7 +1468,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
@@ -1481,11 +1493,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>31.9431209564209</v>
+        <v>31.9431037902832</v>
       </c>
       <c r="C53" t="n">
         <v>43.70000076293945</v>
@@ -1506,11 +1518,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>28.94615936279297</v>
+        <v>28.9461612701416</v>
       </c>
       <c r="C54" t="n">
         <v>39.59999847412109</v>
@@ -1531,11 +1543,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>27.48422431945801</v>
+        <v>27.48422050476074</v>
       </c>
       <c r="C55" t="n">
         <v>37.59999847412109</v>
@@ -1556,11 +1568,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>29.96950531005859</v>
+        <v>29.96951484680176</v>
       </c>
       <c r="C56" t="n">
         <v>41</v>
@@ -1581,7 +1593,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
@@ -1606,11 +1618,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>28.5806713104248</v>
+        <v>28.58067893981934</v>
       </c>
       <c r="C58" t="n">
         <v>39.09999847412109</v>
@@ -1631,11 +1643,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>30.48117256164551</v>
+        <v>30.48118209838867</v>
       </c>
       <c r="C59" t="n">
         <v>41.70000076293945</v>
@@ -1656,11 +1668,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>30.70047760009766</v>
+        <v>30.70046615600586</v>
       </c>
       <c r="C60" t="n">
         <v>42</v>
@@ -1681,11 +1693,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>34.57455825805664</v>
+        <v>34.57457733154297</v>
       </c>
       <c r="C61" t="n">
         <v>47.29999923706055</v>
@@ -1706,11 +1718,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>35.23244094848633</v>
+        <v>35.23245239257812</v>
       </c>
       <c r="C62" t="n">
         <v>48.20000076293945</v>
@@ -1731,11 +1743,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>34.20909118652344</v>
+        <v>34.20908355712891</v>
       </c>
       <c r="C63" t="n">
         <v>46.79999923706055</v>
@@ -1760,11 +1772,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>32.30857849121094</v>
+        <v>32.30859375</v>
       </c>
       <c r="C64" t="n">
         <v>44.20000076293945</v>
@@ -1789,11 +1801,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>33.55124282836914</v>
+        <v>33.55123138427734</v>
       </c>
       <c r="C65" t="n">
         <v>45.90000152587891</v>
@@ -1818,11 +1830,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>30.08658027648926</v>
+        <v>30.08658409118652</v>
       </c>
       <c r="C66" t="n">
         <v>41.15000152587891</v>
@@ -1847,11 +1859,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>30.44482612609863</v>
+        <v>30.44484519958496</v>
       </c>
       <c r="C67" t="n">
         <v>41.63999938964844</v>
@@ -1876,11 +1888,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>28.03938865661621</v>
+        <v>28.03938484191895</v>
       </c>
       <c r="C68" t="n">
         <v>38.34000015258789</v>
@@ -1905,11 +1917,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>22.70795059204102</v>
+        <v>22.70796012878418</v>
       </c>
       <c r="C69" t="n">
         <v>31.04999923706055</v>
@@ -1934,11 +1946,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>18.7368106842041</v>
+        <v>18.73681259155273</v>
       </c>
       <c r="C70" t="n">
         <v>25.6200008392334</v>
@@ -1963,11 +1975,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>23.10287857055664</v>
+        <v>23.10287475585938</v>
       </c>
       <c r="C71" t="n">
         <v>31.59000015258789</v>
@@ -1992,7 +2004,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
@@ -2021,11 +2033,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>19.24787330627441</v>
+        <v>19.24788665771484</v>
       </c>
       <c r="C73" t="n">
         <v>26.30999946594238</v>
@@ -2050,11 +2062,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>22.47415542602539</v>
+        <v>22.47414779663086</v>
       </c>
       <c r="C74" t="n">
         <v>30.71999931335449</v>
@@ -2079,11 +2091,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>24.38397026062012</v>
+        <v>24.38397407531738</v>
       </c>
       <c r="C75" t="n">
         <v>33.31999969482422</v>
@@ -2108,7 +2120,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
@@ -2137,11 +2149,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>24.1790657043457</v>
+        <v>24.17906761169434</v>
       </c>
       <c r="C77" t="n">
         <v>33.04000091552734</v>
@@ -2166,11 +2178,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>19.40626525878906</v>
+        <v>19.4062614440918</v>
       </c>
       <c r="C78" t="n">
         <v>26.51000022888184</v>
@@ -2195,11 +2207,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>20.06509780883789</v>
+        <v>20.06509971618652</v>
       </c>
       <c r="C79" t="n">
         <v>27.40999984741211</v>
@@ -2224,11 +2236,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>19.86012840270996</v>
+        <v>19.86013603210449</v>
       </c>
       <c r="C80" t="n">
         <v>27.1299991607666</v>
@@ -2253,7 +2265,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
@@ -2282,11 +2294,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>23.9611644744873</v>
+        <v>23.96116065979004</v>
       </c>
       <c r="C82" t="n">
         <v>32.72000122070312</v>
@@ -2311,11 +2323,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>27.38105010986328</v>
+        <v>27.38103866577148</v>
       </c>
       <c r="C83" t="n">
         <v>37.38999938964844</v>
@@ -2340,7 +2352,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
@@ -2369,11 +2381,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>28.97790718078613</v>
+        <v>28.9779167175293</v>
       </c>
       <c r="C85" t="n">
         <v>39.56000137329102</v>
@@ -2398,11 +2410,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>30.88978576660156</v>
+        <v>30.88977813720703</v>
       </c>
       <c r="C86" t="n">
         <v>42.15999984741211</v>
@@ -2427,11 +2439,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>30.75057792663574</v>
+        <v>30.75057601928711</v>
       </c>
       <c r="C87" t="n">
         <v>41.97000122070312</v>
@@ -2456,11 +2468,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>32.41375350952148</v>
+        <v>32.41375732421875</v>
       </c>
       <c r="C88" t="n">
         <v>44.2400016784668</v>
@@ -2485,11 +2497,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>34.18685150146484</v>
+        <v>34.18684387207031</v>
       </c>
       <c r="C89" t="n">
         <v>46.65999984741211</v>
@@ -2514,11 +2526,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>38.10033416748047</v>
+        <v>38.10032653808594</v>
       </c>
       <c r="C90" t="n">
         <v>51.9900016784668</v>
@@ -2543,11 +2555,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>35.15431213378906</v>
+        <v>35.1543083190918</v>
       </c>
       <c r="C91" t="n">
         <v>47.97000122070312</v>
@@ -2572,7 +2584,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
@@ -2601,11 +2613,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>35.42492294311523</v>
+        <v>35.42494201660156</v>
       </c>
       <c r="C93" t="n">
         <v>48.33000183105469</v>
@@ -2630,7 +2642,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
@@ -2659,11 +2671,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>35.7619514465332</v>
+        <v>35.76193237304688</v>
       </c>
       <c r="C95" t="n">
         <v>48.77999877929688</v>
@@ -2688,11 +2700,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>38.79710006713867</v>
+        <v>38.79708480834961</v>
       </c>
       <c r="C96" t="n">
         <v>52.91999816894531</v>
@@ -2717,11 +2729,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>38.20326995849609</v>
+        <v>38.2032585144043</v>
       </c>
       <c r="C97" t="n">
         <v>52.11000061035156</v>
@@ -2746,11 +2758,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>34.77944946289062</v>
+        <v>34.77945709228516</v>
       </c>
       <c r="C98" t="n">
         <v>47.43000030517578</v>
@@ -2775,11 +2787,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>35.65938949584961</v>
+        <v>35.65939331054688</v>
       </c>
       <c r="C99" t="n">
         <v>48.63000106811523</v>
@@ -2804,11 +2816,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>34.90410995483398</v>
+        <v>34.90410614013672</v>
       </c>
       <c r="C100" t="n">
         <v>47.59999847412109</v>
@@ -2833,11 +2845,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>35.13141632080078</v>
+        <v>35.13142776489258</v>
       </c>
       <c r="C101" t="n">
         <v>47.90999984741211</v>
@@ -2862,11 +2874,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>34.88938903808594</v>
+        <v>34.8893928527832</v>
       </c>
       <c r="C102" t="n">
         <v>47.56999969482422</v>
@@ -2891,11 +2903,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>34.54467391967773</v>
+        <v>34.54468536376953</v>
       </c>
       <c r="C103" t="n">
         <v>47.09999847412109</v>
@@ -2920,7 +2932,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
@@ -2949,11 +2961,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>37.88937759399414</v>
+        <v>37.88938522338867</v>
       </c>
       <c r="C105" t="n">
         <v>51.65000152587891</v>
@@ -2978,11 +2990,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>38.01408386230469</v>
+        <v>38.01408767700195</v>
       </c>
       <c r="C106" t="n">
         <v>51.81999969482422</v>
@@ -3007,11 +3019,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>39.27597045898438</v>
+        <v>39.27597427368164</v>
       </c>
       <c r="C107" t="n">
         <v>53.52999877929688</v>
@@ -3036,11 +3048,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>39.59880065917969</v>
+        <v>39.59880828857422</v>
       </c>
       <c r="C108" t="n">
         <v>53.97000122070312</v>
@@ -3065,11 +3077,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>39.70151138305664</v>
+        <v>39.70153427124023</v>
       </c>
       <c r="C109" t="n">
         <v>54.11000061035156</v>
@@ -3094,7 +3106,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
@@ -3123,7 +3135,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
@@ -3152,11 +3164,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>37.8092041015625</v>
+        <v>37.80920791625977</v>
       </c>
       <c r="C112" t="n">
         <v>51.52000045776367</v>
@@ -3181,11 +3193,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>39.13019943237305</v>
+        <v>39.13018798828125</v>
       </c>
       <c r="C113" t="n">
         <v>53.31999969482422</v>
@@ -3210,11 +3222,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>39.72555160522461</v>
+        <v>39.72554397583008</v>
       </c>
       <c r="C114" t="n">
         <v>54.08000183105469</v>
@@ -3239,11 +3251,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>40.5776481628418</v>
+        <v>40.57764434814453</v>
       </c>
       <c r="C115" t="n">
         <v>55.2400016784668</v>
@@ -3268,11 +3280,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>42.97942733764648</v>
+        <v>42.97943496704102</v>
       </c>
       <c r="C116" t="n">
         <v>58.45999908447266</v>
@@ -3297,7 +3309,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
@@ -3326,11 +3338,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>36.47295761108398</v>
+        <v>36.47296524047852</v>
       </c>
       <c r="C118" t="n">
         <v>49.61000061035156</v>
@@ -3355,11 +3367,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>39.12600708007812</v>
+        <v>39.12599945068359</v>
       </c>
       <c r="C119" t="n">
         <v>53.16999816894531</v>
@@ -3384,11 +3396,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>39.80300140380859</v>
+        <v>39.80300903320312</v>
       </c>
       <c r="C120" t="n">
         <v>54.09000015258789</v>
@@ -3413,11 +3425,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>38.08108520507812</v>
+        <v>38.08106231689453</v>
       </c>
       <c r="C121" t="n">
         <v>51.75</v>
@@ -3442,11 +3454,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>31.37185668945312</v>
+        <v>31.37184906005859</v>
       </c>
       <c r="C122" t="n">
         <v>42.58000183105469</v>
@@ -3471,11 +3483,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>28.62367630004883</v>
+        <v>28.62368202209473</v>
       </c>
       <c r="C123" t="n">
         <v>38.84999847412109</v>
@@ -3500,11 +3512,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>30.76033592224121</v>
+        <v>30.76032829284668</v>
       </c>
       <c r="C124" t="n">
         <v>41.75</v>
@@ -3529,11 +3541,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>34.13397216796875</v>
+        <v>34.13397598266602</v>
       </c>
       <c r="C125" t="n">
         <v>46.27999877929688</v>
@@ -3558,11 +3570,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>34.34787368774414</v>
+        <v>34.34786224365234</v>
       </c>
       <c r="C126" t="n">
         <v>46.56999969482422</v>
@@ -3587,11 +3599,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>31.264892578125</v>
+        <v>31.26488876342773</v>
       </c>
       <c r="C127" t="n">
         <v>42.38999938964844</v>
@@ -3616,11 +3628,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>32.42937850952148</v>
+        <v>32.42938613891602</v>
       </c>
       <c r="C128" t="n">
         <v>43.81000137329102</v>
@@ -3645,11 +3657,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>35.33846282958984</v>
+        <v>35.33845901489258</v>
       </c>
       <c r="C129" t="n">
         <v>47.7400016784668</v>
@@ -3674,11 +3686,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>34.96094131469727</v>
+        <v>34.96095275878906</v>
       </c>
       <c r="C130" t="n">
         <v>47.22999954223633</v>
@@ -3703,11 +3715,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>36.3821907043457</v>
+        <v>36.38218688964844</v>
       </c>
       <c r="C131" t="n">
         <v>49.15000152587891</v>
@@ -3732,11 +3744,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>41.87948608398438</v>
+        <v>41.87947845458984</v>
       </c>
       <c r="C132" t="n">
         <v>56.38999938964844</v>
@@ -3761,11 +3773,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>44.1372184753418</v>
+        <v>44.13721466064453</v>
       </c>
       <c r="C133" t="n">
         <v>59.43000030517578</v>
@@ -3790,11 +3802,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>41.46359634399414</v>
+        <v>41.46358489990234</v>
       </c>
       <c r="C134" t="n">
         <v>55.83000183105469</v>
@@ -3819,11 +3831,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>44.54660034179688</v>
+        <v>44.54659271240234</v>
       </c>
       <c r="C135" t="n">
         <v>59.81000137329102</v>
@@ -3848,7 +3860,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
@@ -3877,11 +3889,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>44.15021896362305</v>
+        <v>44.15023040771484</v>
       </c>
       <c r="C137" t="n">
         <v>59.11999893188477</v>
@@ -3906,7 +3918,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
@@ -3935,11 +3947,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>49.94532012939453</v>
+        <v>49.94531631469727</v>
       </c>
       <c r="C139" t="n">
         <v>66.87999725341797</v>
@@ -3964,11 +3976,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>51.11777877807617</v>
+        <v>51.11775970458984</v>
       </c>
       <c r="C140" t="n">
         <v>68.44999694824219</v>
@@ -3993,11 +4005,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>51.03938293457031</v>
+        <v>51.03940200805664</v>
       </c>
       <c r="C141" t="n">
         <v>68.02999877929688</v>
@@ -4022,11 +4034,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>54.57305908203125</v>
+        <v>54.57306289672852</v>
       </c>
       <c r="C142" t="n">
         <v>72.73999786376953</v>
@@ -4051,11 +4063,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>55.14323043823242</v>
+        <v>55.14325714111328</v>
       </c>
       <c r="C143" t="n">
         <v>73.5</v>
@@ -4080,11 +4092,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>56.88730621337891</v>
+        <v>56.88731002807617</v>
       </c>
       <c r="C144" t="n">
         <v>75.5</v>
@@ -4109,7 +4121,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
@@ -4138,11 +4150,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>59.13265228271484</v>
+        <v>59.13267135620117</v>
       </c>
       <c r="C146" t="n">
         <v>78.48000335693359</v>
@@ -4167,7 +4179,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
@@ -4194,11 +4206,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>51.06584167480469</v>
+        <v>51.06583786010742</v>
       </c>
       <c r="C148" t="n">
         <v>67.5</v>
@@ -4221,11 +4233,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>51.64836883544922</v>
+        <v>51.64836120605469</v>
       </c>
       <c r="C149" t="n">
         <v>68.26999664306641</v>
@@ -4248,11 +4260,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>50.69181823730469</v>
+        <v>50.69181060791016</v>
       </c>
       <c r="C150" t="n">
         <v>66.69000244140625</v>
@@ -4275,11 +4287,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>50.86664581298828</v>
+        <v>50.86664199829102</v>
       </c>
       <c r="C151" t="n">
         <v>66.91999816894531</v>
@@ -4302,11 +4314,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>54.64439010620117</v>
+        <v>54.64438629150391</v>
       </c>
       <c r="C152" t="n">
         <v>71.88999938964844</v>
@@ -4329,11 +4341,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>54.49164581298828</v>
+        <v>54.49165344238281</v>
       </c>
       <c r="C153" t="n">
         <v>71.23999786376953</v>
@@ -4356,11 +4368,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>54.87410354614258</v>
+        <v>54.87411117553711</v>
       </c>
       <c r="C154" t="n">
         <v>71.73999786376953</v>
@@ -4383,7 +4395,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
@@ -4410,11 +4422,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>49.89912414550781</v>
+        <v>49.89912796020508</v>
       </c>
       <c r="C156" t="n">
         <v>64.79000091552734</v>
@@ -4437,11 +4449,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>40.09490966796875</v>
+        <v>40.09490585327148</v>
       </c>
       <c r="C157" t="n">
         <v>52.06000137329102</v>
@@ -4464,11 +4476,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>49.64496612548828</v>
+        <v>49.64497756958008</v>
       </c>
       <c r="C158" t="n">
         <v>64.45999908447266</v>
@@ -4491,11 +4503,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>49.6217041015625</v>
+        <v>49.62170791625977</v>
       </c>
       <c r="C159" t="n">
         <v>63.97999954223633</v>
@@ -4520,11 +4532,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>48.25667572021484</v>
+        <v>48.25669479370117</v>
       </c>
       <c r="C160" t="n">
         <v>62.22000122070312</v>
@@ -4549,11 +4561,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>54.83361053466797</v>
+        <v>54.83361434936523</v>
       </c>
       <c r="C161" t="n">
         <v>70.69999694824219</v>
@@ -4578,11 +4590,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>48.51266098022461</v>
+        <v>48.51266479492188</v>
       </c>
       <c r="C162" t="n">
         <v>62.15000152587891</v>
@@ -4607,11 +4619,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>54.66357803344727</v>
+        <v>54.6635856628418</v>
       </c>
       <c r="C163" t="n">
         <v>70.02999877929688</v>
@@ -4636,11 +4648,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>55.54565048217773</v>
+        <v>55.54563140869141</v>
       </c>
       <c r="C164" t="n">
         <v>71.16000366210938</v>
@@ -4665,11 +4677,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>50.60754013061523</v>
+        <v>50.60755157470703</v>
       </c>
       <c r="C165" t="n">
         <v>64.34999847412109</v>
@@ -4694,11 +4706,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>54.32742309570312</v>
+        <v>54.32740783691406</v>
       </c>
       <c r="C166" t="n">
         <v>69.08000183105469</v>
@@ -4723,11 +4735,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>56.51371383666992</v>
+        <v>56.51372528076172</v>
       </c>
       <c r="C167" t="n">
         <v>71.86000061035156</v>
@@ -4752,11 +4764,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>59.49979782104492</v>
+        <v>59.49981307983398</v>
       </c>
       <c r="C168" t="n">
         <v>75.12000274658203</v>
@@ -4781,11 +4793,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>63.27795791625977</v>
+        <v>63.27793121337891</v>
       </c>
       <c r="C169" t="n">
         <v>79.88999938964844</v>
@@ -4810,11 +4822,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>59.32822036743164</v>
+        <v>59.32820892333984</v>
       </c>
       <c r="C170" t="n">
         <v>74.41000366210938</v>
@@ -4839,11 +4851,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>50.59761047363281</v>
+        <v>50.59760665893555</v>
       </c>
       <c r="C171" t="n">
         <v>63.45999908447266</v>
@@ -4868,11 +4880,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>33.58290863037109</v>
+        <v>33.58290481567383</v>
       </c>
       <c r="C172" t="n">
         <v>42.11999893188477</v>
@@ -4897,11 +4909,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>38.71762084960938</v>
+        <v>38.71762466430664</v>
       </c>
       <c r="C173" t="n">
         <v>48.56000137329102</v>
@@ -4926,11 +4938,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>38.60480880737305</v>
+        <v>38.60480499267578</v>
       </c>
       <c r="C174" t="n">
         <v>47.90999984741211</v>
@@ -4955,11 +4967,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>41.17524337768555</v>
+        <v>41.17522811889648</v>
       </c>
       <c r="C175" t="n">
         <v>51.09999847412109</v>
@@ -4984,11 +4996,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>40.70502853393555</v>
+        <v>40.70503234863281</v>
       </c>
       <c r="C176" t="n">
         <v>50.0099983215332</v>
@@ -5013,11 +5025,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>41.60850524902344</v>
+        <v>41.60850143432617</v>
       </c>
       <c r="C177" t="n">
         <v>51.11999893188477</v>
@@ -5042,11 +5054,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>35.08886337280273</v>
+        <v>35.08885192871094</v>
       </c>
       <c r="C178" t="n">
         <v>43.11000061035156</v>
@@ -5071,11 +5083,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>34.13113784790039</v>
+        <v>34.13113403320312</v>
       </c>
       <c r="C179" t="n">
         <v>41.41999816894531</v>
@@ -5100,11 +5112,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>45.37909317016602</v>
+        <v>45.37908935546875</v>
       </c>
       <c r="C180" t="n">
         <v>55.06999969482422</v>
@@ -5129,7 +5141,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
@@ -5158,11 +5170,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>48.19256973266602</v>
+        <v>48.19256591796875</v>
       </c>
       <c r="C182" t="n">
         <v>57.9900016784668</v>
@@ -5187,11 +5199,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>54.74954605102539</v>
+        <v>54.74955368041992</v>
       </c>
       <c r="C183" t="n">
         <v>65.87999725341797</v>
@@ -5216,11 +5228,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>60.45885848999023</v>
+        <v>60.4588508605957</v>
       </c>
       <c r="C184" t="n">
         <v>72.75</v>
@@ -5245,7 +5257,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
@@ -5274,11 +5286,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>65.86682891845703</v>
+        <v>65.86684417724609</v>
       </c>
       <c r="C186" t="n">
         <v>78.70999908447266</v>
@@ -5303,11 +5315,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>59.20567321777344</v>
+        <v>59.2056770324707</v>
       </c>
       <c r="C187" t="n">
         <v>70.75</v>
@@ -5332,7 +5344,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
@@ -5361,11 +5373,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>60.62575531005859</v>
+        <v>60.6257438659668</v>
       </c>
       <c r="C189" t="n">
         <v>71.91000366210938</v>
@@ -5390,7 +5402,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
@@ -5419,11 +5431,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>58.7298583984375</v>
+        <v>58.7298698425293</v>
       </c>
       <c r="C191" t="n">
         <v>69.16000366210938</v>
@@ -5448,11 +5460,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>54.09328842163086</v>
+        <v>54.09328460693359</v>
       </c>
       <c r="C192" t="n">
         <v>63.70000076293945</v>
@@ -5477,7 +5489,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
@@ -5506,11 +5518,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>55.29914855957031</v>
+        <v>55.29914093017578</v>
       </c>
       <c r="C194" t="n">
         <v>65.12000274658203</v>
@@ -5535,11 +5547,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>50.69358444213867</v>
+        <v>50.69358062744141</v>
       </c>
       <c r="C195" t="n">
         <v>59.22999954223633</v>
@@ -5564,11 +5576,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>45.70382690429688</v>
+        <v>45.70382308959961</v>
       </c>
       <c r="C196" t="n">
         <v>53.40000152587891</v>
@@ -5593,11 +5605,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>41.68685531616211</v>
+        <v>41.68685913085938</v>
       </c>
       <c r="C197" t="n">
         <v>48.20999908447266</v>
@@ -5622,11 +5634,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>46.18325424194336</v>
+        <v>46.18326187133789</v>
       </c>
       <c r="C198" t="n">
         <v>53.40999984741211</v>
@@ -5651,11 +5663,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>39.76723098754883</v>
+        <v>39.76724624633789</v>
       </c>
       <c r="C199" t="n">
         <v>45.9900016784668</v>
@@ -5680,11 +5692,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>45.32011413574219</v>
+        <v>45.32010269165039</v>
       </c>
       <c r="C200" t="n">
         <v>51.90000152587891</v>
@@ -5709,11 +5721,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>42.62185287475586</v>
+        <v>42.62184906005859</v>
       </c>
       <c r="C201" t="n">
         <v>48.81000137329102</v>
@@ -5738,11 +5750,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>36.38706588745117</v>
+        <v>36.38705444335938</v>
       </c>
       <c r="C202" t="n">
         <v>41.66999816894531</v>
@@ -5767,11 +5779,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>40.04586029052734</v>
+        <v>40.04585647583008</v>
       </c>
       <c r="C203" t="n">
         <v>45.86000061035156</v>
@@ -5796,11 +5808,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>42.76176452636719</v>
+        <v>42.76176834106445</v>
       </c>
       <c r="C204" t="n">
         <v>48.40999984741211</v>
@@ -5825,11 +5837,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>39.95278930664062</v>
+        <v>39.95278549194336</v>
       </c>
       <c r="C205" t="n">
         <v>45.22999954223633</v>
@@ -5854,11 +5866,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>46.12723922729492</v>
+        <v>46.12723159790039</v>
       </c>
       <c r="C206" t="n">
         <v>52.22000122070312</v>
@@ -5883,11 +5895,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>45.21735000610352</v>
+        <v>45.21735382080078</v>
       </c>
       <c r="C207" t="n">
         <v>50.68999862670898</v>
@@ -5912,7 +5924,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -5941,11 +5953,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>42.44850158691406</v>
+        <v>42.4484977722168</v>
       </c>
       <c r="C209" t="n">
         <v>47.06999969482422</v>
@@ -5970,11 +5982,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>39.968505859375</v>
+        <v>39.96850204467773</v>
       </c>
       <c r="C210" t="n">
         <v>44.31999969482422</v>
@@ -5999,11 +6011,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>41.51962661743164</v>
+        <v>41.51963043212891</v>
       </c>
       <c r="C211" t="n">
         <v>46.04000091552734</v>
@@ -6028,11 +6040,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>42.9805793762207</v>
+        <v>42.98057556152344</v>
       </c>
       <c r="C212" t="n">
         <v>47.65999984741211</v>
@@ -6057,11 +6069,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>37.66802597045898</v>
+        <v>37.66802978515625</v>
       </c>
       <c r="C213" t="n">
         <v>41.29000091552734</v>
@@ -6086,11 +6098,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>37.52206420898438</v>
+        <v>37.52206802368164</v>
       </c>
       <c r="C214" t="n">
         <v>41.13000106811523</v>
@@ -6115,7 +6127,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
@@ -6144,11 +6156,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>42.60214233398438</v>
+        <v>42.60214614868164</v>
       </c>
       <c r="C216" t="n">
         <v>46.09999847412109</v>
@@ -6173,11 +6185,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>47.53696823120117</v>
+        <v>47.53697204589844</v>
       </c>
       <c r="C217" t="n">
         <v>51.43999862670898</v>
@@ -6202,7 +6214,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6231,11 +6243,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>51.76910400390625</v>
+        <v>51.76910018920898</v>
       </c>
       <c r="C219" t="n">
         <v>55.4900016784668</v>
@@ -6260,7 +6272,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6289,11 +6301,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>57.21750259399414</v>
+        <v>57.21749877929688</v>
       </c>
       <c r="C221" t="n">
         <v>61.33000183105469</v>
@@ -6318,7 +6330,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -6347,7 +6359,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
@@ -6376,11 +6388,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>61.05527877807617</v>
+        <v>61.05527496337891</v>
       </c>
       <c r="C224" t="n">
         <v>64.87999725341797</v>
@@ -6405,11 +6417,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>59.51451873779297</v>
+        <v>59.5145263671875</v>
       </c>
       <c r="C225" t="n">
         <v>62.63999938964844</v>
@@ -6434,11 +6446,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>59.47652053833008</v>
+        <v>59.47651672363281</v>
       </c>
       <c r="C226" t="n">
         <v>62.59999847412109</v>
@@ -6463,7 +6475,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6492,7 +6504,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -6521,11 +6533,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>67.47088623046875</v>
+        <v>67.47087860107422</v>
       </c>
       <c r="C229" t="n">
         <v>70.38999938964844</v>
@@ -6550,11 +6562,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>78.05306243896484</v>
+        <v>78.05304718017578</v>
       </c>
       <c r="C230" t="n">
         <v>81.43000030517578</v>
@@ -6579,7 +6591,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6608,7 +6620,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -6637,11 +6649,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>65.99810791015625</v>
+        <v>65.99811553955078</v>
       </c>
       <c r="C233" t="n">
         <v>68.37999725341797</v>
@@ -6666,11 +6678,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>73.27770233154297</v>
+        <v>73.27769470214844</v>
       </c>
       <c r="C234" t="n">
         <v>75.31999969482422</v>
@@ -6695,7 +6707,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6724,7 +6736,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6753,7 +6765,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6782,7 +6794,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6811,7 +6823,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6840,7 +6852,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6869,11 +6881,11 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>114.9539260864258</v>
+        <v>114.9539184570312</v>
       </c>
       <c r="C241" t="n">
         <v>116.6900024414062</v>
@@ -6898,7 +6910,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6927,7 +6939,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6956,7 +6968,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -6985,7 +6997,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7014,7 +7026,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7043,7 +7055,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7072,7 +7084,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7101,7 +7113,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7130,23 +7142,23 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>131.9299926757812</v>
+        <v>132.1000061035156</v>
       </c>
       <c r="C250" t="n">
-        <v>131.9299926757812</v>
+        <v>132.1000061035156</v>
       </c>
       <c r="D250" t="n">
-        <v>158583200</v>
+        <v>167231200</v>
       </c>
       <c r="E250" t="n">
         <v>9.280000000000001</v>
       </c>
       <c r="F250" t="n">
-        <v>14.2165940383385</v>
+        <v>14.23491445080987</v>
       </c>
       <c r="G250" t="inlineStr"/>
       <c r="H250" t="inlineStr"/>
@@ -7181,75 +7193,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7285,13 +7297,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7327,13 +7339,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40396</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7369,13 +7381,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7411,13 +7423,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7444,7 +7456,7 @@
       <c r="I6" t="n">
         <v>-2.9</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K6" t="n">
@@ -7457,13 +7469,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7490,7 +7502,7 @@
       <c r="I7" t="n">
         <v>0.3999999999999992</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K7" t="n">
@@ -7503,13 +7515,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40396</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7536,7 +7548,7 @@
       <c r="I8" t="n">
         <v>-3.6</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K8" t="n">
@@ -7549,13 +7561,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7582,7 +7594,7 @@
       <c r="I9" t="n">
         <v>-0.1999999999999998</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K9" t="n">
@@ -7595,13 +7607,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7628,7 +7640,7 @@
       <c r="I10" t="n">
         <v>3.5</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K10" t="n">
@@ -7641,13 +7653,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40668</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7674,7 +7686,7 @@
       <c r="I11" t="n">
         <v>3</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40668</v>
       </c>
       <c r="K11" t="n">
@@ -7687,13 +7699,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7720,7 +7732,7 @@
       <c r="I12" t="n">
         <v>3.19</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="K12" t="n">
@@ -7733,13 +7745,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7766,7 +7778,7 @@
       <c r="I13" t="n">
         <v>3.720000000000001</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="K13" t="n">
@@ -7779,13 +7791,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7812,7 +7824,7 @@
       <c r="I14" t="n">
         <v>3.63</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="K14" t="n">
@@ -7825,13 +7837,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41033</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7858,7 +7870,7 @@
       <c r="I15" t="n">
         <v>3.58</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41033</v>
       </c>
       <c r="K15" t="n">
@@ -7871,13 +7883,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41124</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7904,7 +7916,7 @@
       <c r="I16" t="n">
         <v>3.44</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41124</v>
       </c>
       <c r="K16" t="n">
@@ -7917,13 +7929,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41219</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7950,7 +7962,7 @@
       <c r="I17" t="n">
         <v>2.36</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41219</v>
       </c>
       <c r="K17" t="n">
@@ -7963,13 +7975,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7996,7 +8008,7 @@
       <c r="I18" t="n">
         <v>2.43</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="K18" t="n">
@@ -8009,13 +8021,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41397</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8042,7 +8054,7 @@
       <c r="I19" t="n">
         <v>2.71</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41397</v>
       </c>
       <c r="K19" t="n">
@@ -8055,13 +8067,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41488</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8088,7 +8100,7 @@
       <c r="I20" t="n">
         <v>3.100000000000001</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41488</v>
       </c>
       <c r="K20" t="n">
@@ -8101,13 +8113,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8134,7 +8146,7 @@
       <c r="I21" t="n">
         <v>3.95</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="K21" t="n">
@@ -8147,13 +8159,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41701</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8180,7 +8192,7 @@
       <c r="I22" t="n">
         <v>4.340000000000001</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41701</v>
       </c>
       <c r="K22" t="n">
@@ -8193,13 +8205,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41761</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8226,7 +8238,7 @@
       <c r="I23" t="n">
         <v>4.34</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41761</v>
       </c>
       <c r="K23" t="n">
@@ -8239,13 +8251,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41852</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8272,7 +8284,7 @@
       <c r="I24" t="n">
         <v>3.03</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41852</v>
       </c>
       <c r="K24" t="n">
@@ -8285,13 +8297,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41942</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8318,7 +8330,7 @@
       <c r="I25" t="n">
         <v>2.91</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41942</v>
       </c>
       <c r="K25" t="n">
@@ -8331,13 +8343,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42060</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8364,7 +8376,7 @@
       <c r="I26" t="n">
         <v>2.2</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42060</v>
       </c>
       <c r="K26" t="n">
@@ -8377,13 +8389,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42135</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8410,7 +8422,7 @@
       <c r="I27" t="n">
         <v>2.48</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42135</v>
       </c>
       <c r="K27" t="n">
@@ -8423,13 +8435,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42219</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8456,7 +8468,7 @@
       <c r="I28" t="n">
         <v>3.96</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42219</v>
       </c>
       <c r="K28" t="n">
@@ -8469,13 +8481,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8502,7 +8514,7 @@
       <c r="I29" t="n">
         <v>4.43</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="K29" t="n">
@@ -8515,13 +8527,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8548,7 +8560,7 @@
       <c r="I30" t="n">
         <v>5.390000000000001</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="K30" t="n">
@@ -8561,13 +8573,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42492</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8594,7 +8606,7 @@
       <c r="I31" t="n">
         <v>4.98</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42492</v>
       </c>
       <c r="K31" t="n">
@@ -8607,13 +8619,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42583</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8640,7 +8652,7 @@
       <c r="I32" t="n">
         <v>4.710000000000001</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42583</v>
       </c>
       <c r="K32" t="n">
@@ -8653,13 +8665,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8686,7 +8698,7 @@
       <c r="I33" t="n">
         <v>4.6</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="K33" t="n">
@@ -8699,13 +8711,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42790</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8732,7 +8744,7 @@
       <c r="I34" t="n">
         <v>4.720000000000001</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42790</v>
       </c>
       <c r="K34" t="n">
@@ -8745,13 +8757,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42856</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8778,7 +8790,7 @@
       <c r="I35" t="n">
         <v>4.97</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42856</v>
       </c>
       <c r="K35" t="n">
@@ -8791,13 +8803,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8824,7 +8836,7 @@
       <c r="I36" t="n">
         <v>5.01</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="K36" t="n">
@@ -8837,13 +8849,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8870,7 +8882,7 @@
       <c r="I37" t="n">
         <v>5.19</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="K37" t="n">
@@ -8883,13 +8895,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43154</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8916,7 +8928,7 @@
       <c r="I38" t="n">
         <v>-3.329999999999999</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43154</v>
       </c>
       <c r="K38" t="n">
@@ -8929,13 +8941,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8962,7 +8974,7 @@
       <c r="I39" t="n">
         <v>-3</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="K39" t="n">
@@ -8975,13 +8987,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9008,7 +9020,7 @@
       <c r="I40" t="n">
         <v>-2.649999999999999</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="K40" t="n">
@@ -9021,13 +9033,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43403</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9054,7 +9066,7 @@
       <c r="I41" t="n">
         <v>-2.339999999999999</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43403</v>
       </c>
       <c r="K41" t="n">
@@ -9067,13 +9079,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43518</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9100,7 +9112,7 @@
       <c r="I42" t="n">
         <v>6.680000000000001</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43518</v>
       </c>
       <c r="K42" t="n">
@@ -9113,13 +9125,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9146,7 +9158,7 @@
       <c r="I43" t="n">
         <v>6.870000000000001</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="K43" t="n">
@@ -9159,13 +9171,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9192,7 +9204,7 @@
       <c r="I44" t="n">
         <v>7.190000000000001</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="K44" t="n">
@@ -9205,13 +9217,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9238,7 +9250,7 @@
       <c r="I45" t="n">
         <v>7.53</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="K45" t="n">
@@ -9251,13 +9263,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43882</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9284,7 +9296,7 @@
       <c r="I46" t="n">
         <v>8.040000000000001</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43882</v>
       </c>
       <c r="K46" t="n">
@@ -9297,13 +9309,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43955</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9330,7 +9342,7 @@
       <c r="I47" t="n">
         <v>7.220000000000001</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43955</v>
       </c>
       <c r="K47" t="n">
@@ -9343,13 +9355,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44048</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9376,7 +9388,7 @@
       <c r="I48" t="n">
         <v>5.77</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44048</v>
       </c>
       <c r="K48" t="n">
@@ -9389,13 +9401,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44139</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9422,7 +9434,7 @@
       <c r="I49" t="n">
         <v>5.100000000000001</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44139</v>
       </c>
       <c r="K49" t="n">
@@ -9435,13 +9447,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44253</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9468,7 +9480,7 @@
       <c r="I50" t="n">
         <v>4.870000000000001</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44253</v>
       </c>
       <c r="K50" t="n">
@@ -9481,13 +9493,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9514,7 +9526,7 @@
       <c r="I51" t="n">
         <v>7.440000000000001</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="K51" t="n">
@@ -9527,13 +9539,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9560,7 +9572,7 @@
       <c r="I52" t="n">
         <v>9.790000000000001</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="K52" t="n">
@@ -9573,13 +9585,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44508</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9606,7 +9618,7 @@
       <c r="I53" t="n">
         <v>10.54</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44508</v>
       </c>
       <c r="K53" t="n">
@@ -9619,13 +9631,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9652,7 +9664,7 @@
       <c r="I54" t="n">
         <v>10.08</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="K54" t="n">
@@ -9665,13 +9677,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44690</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9698,7 +9710,7 @@
       <c r="I55" t="n">
         <v>8.48</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44690</v>
       </c>
       <c r="K55" t="n">
@@ -9711,13 +9723,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9744,7 +9756,7 @@
       <c r="I56" t="n">
         <v>7.820000000000001</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="K56" t="n">
@@ -9757,13 +9769,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44869</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9790,7 +9802,7 @@
       <c r="I57" t="n">
         <v>7.300000000000001</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44869</v>
       </c>
       <c r="K57" t="n">
@@ -9803,13 +9815,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44984</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9836,7 +9848,7 @@
       <c r="I58" t="n">
         <v>7.000000000000001</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44984</v>
       </c>
       <c r="K58" t="n">
@@ -9849,13 +9861,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45051</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9882,7 +9894,7 @@
       <c r="I59" t="n">
         <v>7.17</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45051</v>
       </c>
       <c r="K59" t="n">
@@ -9895,13 +9907,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9928,7 +9940,7 @@
       <c r="I60" t="n">
         <v>6.31</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="K60" t="n">
@@ -9941,13 +9953,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45233</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9974,7 +9986,7 @@
       <c r="I61" t="n">
         <v>6.31</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45233</v>
       </c>
       <c r="K61" t="n">
@@ -9987,13 +9999,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45345</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10020,7 +10032,7 @@
       <c r="I62" t="n">
         <v>4.040000000000001</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45345</v>
       </c>
       <c r="K62" t="n">
@@ -10033,13 +10045,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45415</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10066,7 +10078,7 @@
       <c r="I63" t="n">
         <v>3.430000000000001</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45415</v>
       </c>
       <c r="K63" t="n">
@@ -10079,13 +10091,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10112,7 +10124,7 @@
       <c r="I64" t="n">
         <v>3.620000000000001</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="K64" t="n">
@@ -10125,13 +10137,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45603</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10158,7 +10170,7 @@
       <c r="I65" t="n">
         <v>3.500000000000001</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45603</v>
       </c>
       <c r="K65" t="n">
@@ -10171,13 +10183,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10204,7 +10216,7 @@
       <c r="I66" t="n">
         <v>5.940000000000001</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="K66" t="n">
@@ -10217,13 +10229,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45785</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10250,7 +10262,7 @@
       <c r="I67" t="n">
         <v>6.320000000000001</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45785</v>
       </c>
       <c r="K67" t="n">
@@ -10263,13 +10275,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10296,7 +10308,7 @@
       <c r="I68" t="n">
         <v>6.760000000000001</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="K68" t="n">
@@ -10309,13 +10321,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10342,7 +10354,7 @@
       <c r="I69" t="n">
         <v>7.110000000000001</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="K69" t="n">
@@ -10355,13 +10367,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>46073</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10388,7 +10400,7 @@
       <c r="I70" t="n">
         <v>6.99</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>46073</v>
       </c>
       <c r="K70" t="n">
@@ -10401,13 +10413,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10428,7 +10440,7 @@
       <c r="I71" t="n">
         <v>8.09</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="K71" t="n">
@@ -10441,13 +10453,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10468,7 +10480,7 @@
       <c r="I72" t="n">
         <v>9.280000000000001</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="K72" t="n">
@@ -10505,52 +10517,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="C2" t="n">
@@ -10579,10 +10591,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40209</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40235</v>
       </c>
       <c r="C3" t="n">
@@ -10611,10 +10623,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40298</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="C4" t="n">
@@ -10643,10 +10655,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40390</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40396</v>
       </c>
       <c r="C5" t="n">
@@ -10675,10 +10687,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40482</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="C6" t="n">
@@ -10707,10 +10719,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40574</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="C7" t="n">
@@ -10739,10 +10751,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40668</v>
       </c>
       <c r="C8" t="n">
@@ -10771,10 +10783,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="C9" t="n">
@@ -10803,10 +10815,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="C10" t="n">
@@ -10835,10 +10847,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="C11" t="n">
@@ -10867,10 +10879,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41033</v>
       </c>
       <c r="C12" t="n">
@@ -10899,10 +10911,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41124</v>
       </c>
       <c r="C13" t="n">
@@ -10931,10 +10943,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41219</v>
       </c>
       <c r="C14" t="n">
@@ -10963,10 +10975,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="C15" t="n">
@@ -10995,10 +11007,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41397</v>
       </c>
       <c r="C16" t="n">
@@ -11027,10 +11039,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41488</v>
       </c>
       <c r="C17" t="n">
@@ -11059,10 +11071,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="C18" t="n">
@@ -11091,10 +11103,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41701</v>
       </c>
       <c r="C19" t="n">
@@ -11123,10 +11135,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41761</v>
       </c>
       <c r="C20" t="n">
@@ -11155,10 +11167,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41852</v>
       </c>
       <c r="C21" t="n">
@@ -11187,10 +11199,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41942</v>
       </c>
       <c r="C22" t="n">
@@ -11219,10 +11231,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42035</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42060</v>
       </c>
       <c r="C23" t="n">
@@ -11251,10 +11263,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42135</v>
       </c>
       <c r="C24" t="n">
@@ -11283,10 +11295,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42219</v>
       </c>
       <c r="C25" t="n">
@@ -11315,10 +11327,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="C26" t="n">
@@ -11347,10 +11359,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="C27" t="n">
@@ -11379,10 +11391,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42492</v>
       </c>
       <c r="C28" t="n">
@@ -11411,10 +11423,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42583</v>
       </c>
       <c r="C29" t="n">
@@ -11443,10 +11455,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="C30" t="n">
@@ -11475,10 +11487,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42766</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42790</v>
       </c>
       <c r="C31" t="n">
@@ -11507,10 +11519,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42856</v>
       </c>
       <c r="C32" t="n">
@@ -11539,10 +11551,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="C33" t="n">
@@ -11571,10 +11583,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="C34" t="n">
@@ -11603,10 +11615,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43131</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43154</v>
       </c>
       <c r="C35" t="n">
@@ -11635,10 +11647,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="C36" t="n">
@@ -11667,10 +11679,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="C37" t="n">
@@ -11699,10 +11711,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43403</v>
       </c>
       <c r="C38" t="n">
@@ -11731,10 +11743,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43496</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43518</v>
       </c>
       <c r="C39" t="n">
@@ -11763,10 +11775,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="C40" t="n">
@@ -11795,10 +11807,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="C41" t="n">
@@ -11827,10 +11839,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="C42" t="n">
@@ -11859,10 +11871,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43882</v>
       </c>
       <c r="C43" t="n">
@@ -11891,10 +11903,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43955</v>
       </c>
       <c r="C44" t="n">
@@ -11923,10 +11935,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44048</v>
       </c>
       <c r="C45" t="n">
@@ -11955,10 +11967,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44139</v>
       </c>
       <c r="C46" t="n">
@@ -11987,10 +11999,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44227</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44253</v>
       </c>
       <c r="C47" t="n">
@@ -12019,10 +12031,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="C48" t="n">
@@ -12051,10 +12063,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="C49" t="n">
@@ -12083,10 +12095,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44508</v>
       </c>
       <c r="C50" t="n">
@@ -12115,10 +12127,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="C51" t="n">
@@ -12147,10 +12159,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44690</v>
       </c>
       <c r="C52" t="n">
@@ -12179,10 +12191,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="C53" t="n">
@@ -12211,10 +12223,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44869</v>
       </c>
       <c r="C54" t="n">
@@ -12243,10 +12255,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44957</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44984</v>
       </c>
       <c r="C55" t="n">
@@ -12275,10 +12287,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45051</v>
       </c>
       <c r="C56" t="n">
@@ -12307,10 +12319,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="C57" t="n">
@@ -12339,10 +12351,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45233</v>
       </c>
       <c r="C58" t="n">
@@ -12371,10 +12383,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45322</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45345</v>
       </c>
       <c r="C59" t="n">
@@ -12403,10 +12415,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45415</v>
       </c>
       <c r="C60" t="n">
@@ -12435,10 +12447,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="C61" t="n">
@@ -12467,10 +12479,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45603</v>
       </c>
       <c r="C62" t="n">
@@ -12499,10 +12511,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45688</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="C63" t="n">
@@ -12531,10 +12543,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45785</v>
       </c>
       <c r="C64" t="n">
@@ -12563,10 +12575,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="C65" t="n">
@@ -12595,10 +12607,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="C66" t="n">
@@ -12627,10 +12639,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46053</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46073</v>
       </c>
       <c r="C67" t="n">
@@ -12677,12 +12689,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/C.xlsx
+++ b/salidas/empresas/C.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>295.5328369140625</v>
+        <v>295.5328063964844</v>
       </c>
       <c r="C2" t="n">
         <v>465.7999877929688</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>297.3451232910156</v>
+        <v>297.3453063964844</v>
       </c>
       <c r="C3" t="n">
         <v>463.7000122070312</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>302.8600158691406</v>
+        <v>302.8599243164062</v>
       </c>
       <c r="C4" t="n">
         <v>472.2999877929688</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>323.622802734375</v>
+        <v>323.6227111816406</v>
       </c>
       <c r="C5" t="n">
         <v>499.5</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>319.4114074707031</v>
+        <v>319.4114685058594</v>
       </c>
       <c r="C6" t="n">
         <v>493</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>312.608642578125</v>
+        <v>312.6086730957031</v>
       </c>
       <c r="C7" t="n">
         <v>482.5</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>322.9836730957031</v>
+        <v>322.9837036132812</v>
       </c>
       <c r="C9" t="n">
         <v>493.5</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>325.0781860351562</v>
+        <v>325.0782165527344</v>
       </c>
       <c r="C10" t="n">
         <v>496.7000122070312</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>328.2850952148438</v>
+        <v>328.2849426269531</v>
       </c>
       <c r="C11" t="n">
         <v>501.6000061035156</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>327.7607421875</v>
+        <v>327.7608032226562</v>
       </c>
       <c r="C12" t="n">
         <v>495.8999938964844</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>368.1444702148438</v>
+        <v>368.1443176269531</v>
       </c>
       <c r="C13" t="n">
         <v>557</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>364.3768310546875</v>
+        <v>364.376953125</v>
       </c>
       <c r="C14" t="n">
         <v>551.2999877929688</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>336.2093811035156</v>
+        <v>336.2092895507812</v>
       </c>
       <c r="C15" t="n">
         <v>503.7000122070312</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>342.6838684082031</v>
+        <v>342.6838989257812</v>
       </c>
       <c r="C16" t="n">
         <v>513.4000244140625</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>357.9024658203125</v>
+        <v>357.9024353027344</v>
       </c>
       <c r="C17" t="n">
         <v>536.2000122070312</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>367.3629150390625</v>
+        <v>367.3628845214844</v>
       </c>
       <c r="C18" t="n">
         <v>544.9000244140625</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>345.7888488769531</v>
+        <v>345.7890014648438</v>
       </c>
       <c r="C19" t="n">
         <v>512.9000244140625</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>313.9673461914062</v>
+        <v>313.9674072265625</v>
       </c>
       <c r="C20" t="n">
         <v>465.7000122070312</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>319.7428283691406</v>
+        <v>319.742919921875</v>
       </c>
       <c r="C21" t="n">
         <v>468.7999877929688</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>318.310546875</v>
+        <v>318.3105163574219</v>
       </c>
       <c r="C22" t="n">
         <v>466.7000122070312</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>285.7769775390625</v>
+        <v>285.77685546875</v>
       </c>
       <c r="C23" t="n">
         <v>419</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>230.08642578125</v>
+        <v>230.0863952636719</v>
       </c>
       <c r="C24" t="n">
         <v>333</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>203.4156799316406</v>
+        <v>203.4157409667969</v>
       </c>
       <c r="C25" t="n">
         <v>294.3999938964844</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>196.9006500244141</v>
+        <v>196.9006805419922</v>
       </c>
       <c r="C26" t="n">
         <v>281.7000122070312</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>165.7264556884766</v>
+        <v>165.7264404296875</v>
       </c>
       <c r="C27" t="n">
         <v>237.1000061035156</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>149.7200164794922</v>
+        <v>149.7199554443359</v>
       </c>
       <c r="C28" t="n">
         <v>214.1999969482422</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>176.6304321289062</v>
+        <v>176.63037109375</v>
       </c>
       <c r="C29" t="n">
         <v>252.6999969482422</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>154.9674835205078</v>
+        <v>154.967529296875</v>
       </c>
       <c r="C30" t="n">
         <v>218.8999938964844</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>118.6503295898438</v>
+        <v>118.6503601074219</v>
       </c>
       <c r="C31" t="n">
         <v>167.6000061035156</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>134.6034545898438</v>
+        <v>134.6034088134766</v>
       </c>
       <c r="C32" t="n">
         <v>186.8999938964844</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>136.7640228271484</v>
+        <v>136.7640075683594</v>
       </c>
       <c r="C33" t="n">
         <v>189.8999938964844</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>99.53952789306641</v>
+        <v>99.53954315185547</v>
       </c>
       <c r="C35" t="n">
         <v>136.5</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>60.45294570922852</v>
+        <v>60.45294189453125</v>
       </c>
       <c r="C36" t="n">
         <v>82.90000152587891</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>48.9311408996582</v>
+        <v>48.93114471435547</v>
       </c>
       <c r="C37" t="n">
         <v>67.09999847412109</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>25.94921493530273</v>
+        <v>25.94919967651367</v>
       </c>
       <c r="C38" t="n">
         <v>35.5</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>10.96445465087891</v>
+        <v>10.96445274353027</v>
       </c>
       <c r="C39" t="n">
         <v>15</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>18.49337768554688</v>
+        <v>18.49338150024414</v>
       </c>
       <c r="C40" t="n">
         <v>25.29999923706055</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>22.29438400268555</v>
+        <v>22.29439544677734</v>
       </c>
       <c r="C41" t="n">
         <v>30.5</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>27.19184112548828</v>
+        <v>27.19184303283691</v>
       </c>
       <c r="C42" t="n">
         <v>37.20000076293945</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>21.70962142944336</v>
+        <v>21.7096118927002</v>
       </c>
       <c r="C43" t="n">
         <v>29.70000076293945</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>23.17154693603516</v>
+        <v>23.17154121398926</v>
       </c>
       <c r="C44" t="n">
         <v>31.70000076293945</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>36.54817199707031</v>
+        <v>36.54816818237305</v>
       </c>
       <c r="C45" t="n">
         <v>50</v>
@@ -1334,7 +1334,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>35.37864685058594</v>
+        <v>35.37863922119141</v>
       </c>
       <c r="C46" t="n">
         <v>48.40000152587891</v>
@@ -1353,7 +1353,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>29.89641571044922</v>
+        <v>29.89641761779785</v>
       </c>
       <c r="C47" t="n">
         <v>40.90000152587891</v>
@@ -1372,7 +1372,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>30.0425910949707</v>
+        <v>30.04259490966797</v>
       </c>
       <c r="C48" t="n">
         <v>41.09999847412109</v>
@@ -1397,7 +1397,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>24.19489288330078</v>
+        <v>24.19488906860352</v>
       </c>
       <c r="C49" t="n">
         <v>33.09999847412109</v>
@@ -1422,7 +1422,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>24.26799392700195</v>
+        <v>24.26798820495605</v>
       </c>
       <c r="C50" t="n">
         <v>33.20000076293945</v>
@@ -1447,7 +1447,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>24.85276222229004</v>
+        <v>24.85276031494141</v>
       </c>
       <c r="C51" t="n">
         <v>34</v>
@@ -1472,7 +1472,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>29.60401916503906</v>
+        <v>29.60402488708496</v>
       </c>
       <c r="C52" t="n">
         <v>40.5</v>
@@ -1497,7 +1497,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>31.9431037902832</v>
+        <v>31.94311141967773</v>
       </c>
       <c r="C53" t="n">
         <v>43.70000076293945</v>
@@ -1522,7 +1522,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>28.9461612701416</v>
+        <v>28.94616508483887</v>
       </c>
       <c r="C54" t="n">
         <v>39.59999847412109</v>
@@ -1547,7 +1547,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>27.48422050476074</v>
+        <v>27.48423004150391</v>
       </c>
       <c r="C55" t="n">
         <v>37.59999847412109</v>
@@ -1572,7 +1572,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>29.96951484680176</v>
+        <v>29.96950340270996</v>
       </c>
       <c r="C56" t="n">
         <v>41</v>
@@ -1597,7 +1597,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>27.11874008178711</v>
+        <v>27.11874961853027</v>
       </c>
       <c r="C57" t="n">
         <v>37.09999847412109</v>
@@ -1622,7 +1622,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>28.58067893981934</v>
+        <v>28.58067321777344</v>
       </c>
       <c r="C58" t="n">
         <v>39.09999847412109</v>
@@ -1647,7 +1647,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>30.48118209838867</v>
+        <v>30.48118591308594</v>
       </c>
       <c r="C59" t="n">
         <v>41.70000076293945</v>
@@ -1672,7 +1672,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>30.70046615600586</v>
+        <v>30.70047187805176</v>
       </c>
       <c r="C60" t="n">
         <v>42</v>
@@ -1722,7 +1722,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>35.23245239257812</v>
+        <v>35.2324333190918</v>
       </c>
       <c r="C62" t="n">
         <v>48.20000076293945</v>
@@ -1747,7 +1747,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>34.20908355712891</v>
+        <v>34.20910263061523</v>
       </c>
       <c r="C63" t="n">
         <v>46.79999923706055</v>
@@ -1776,7 +1776,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>32.30859375</v>
+        <v>32.3085823059082</v>
       </c>
       <c r="C64" t="n">
         <v>44.20000076293945</v>
@@ -1834,7 +1834,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>30.08658409118652</v>
+        <v>30.08657836914062</v>
       </c>
       <c r="C66" t="n">
         <v>41.15000152587891</v>
@@ -1863,7 +1863,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>30.44484519958496</v>
+        <v>30.44483757019043</v>
       </c>
       <c r="C67" t="n">
         <v>41.63999938964844</v>
@@ -1892,7 +1892,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>28.03938484191895</v>
+        <v>28.03938674926758</v>
       </c>
       <c r="C68" t="n">
         <v>38.34000015258789</v>
@@ -1921,7 +1921,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>22.70796012878418</v>
+        <v>22.70795059204102</v>
       </c>
       <c r="C69" t="n">
         <v>31.04999923706055</v>
@@ -1950,7 +1950,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>18.73681259155273</v>
+        <v>18.73680305480957</v>
       </c>
       <c r="C70" t="n">
         <v>25.6200008392334</v>
@@ -1979,7 +1979,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>23.10287475585938</v>
+        <v>23.10287857055664</v>
       </c>
       <c r="C71" t="n">
         <v>31.59000015258789</v>
@@ -2008,7 +2008,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>20.10382843017578</v>
+        <v>20.10382652282715</v>
       </c>
       <c r="C72" t="n">
         <v>27.47999954223633</v>
@@ -2037,7 +2037,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>19.24788665771484</v>
+        <v>19.24787902832031</v>
       </c>
       <c r="C73" t="n">
         <v>26.30999946594238</v>
@@ -2066,7 +2066,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>22.47414779663086</v>
+        <v>22.47414588928223</v>
       </c>
       <c r="C74" t="n">
         <v>30.71999931335449</v>
@@ -2095,7 +2095,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>24.38397407531738</v>
+        <v>24.38397026062012</v>
       </c>
       <c r="C75" t="n">
         <v>33.31999969482422</v>
@@ -2124,7 +2124,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>26.74772262573242</v>
+        <v>26.74773597717285</v>
       </c>
       <c r="C76" t="n">
         <v>36.54999923706055</v>
@@ -2182,7 +2182,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>19.4062614440918</v>
+        <v>19.40626907348633</v>
       </c>
       <c r="C78" t="n">
         <v>26.51000022888184</v>
@@ -2211,7 +2211,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>20.06509971618652</v>
+        <v>20.06510162353516</v>
       </c>
       <c r="C79" t="n">
         <v>27.40999984741211</v>
@@ -2240,7 +2240,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>19.86013603210449</v>
+        <v>19.86013412475586</v>
       </c>
       <c r="C80" t="n">
         <v>27.1299991607666</v>
@@ -2269,7 +2269,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>21.75691223144531</v>
+        <v>21.75690650939941</v>
       </c>
       <c r="C81" t="n">
         <v>29.70999908447266</v>
@@ -2298,7 +2298,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>23.96116065979004</v>
+        <v>23.96115875244141</v>
       </c>
       <c r="C82" t="n">
         <v>32.72000122070312</v>
@@ -2356,7 +2356,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>25.32269668579102</v>
+        <v>25.32269096374512</v>
       </c>
       <c r="C84" t="n">
         <v>34.56999969482422</v>
@@ -2385,7 +2385,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>28.9779167175293</v>
+        <v>28.97791481018066</v>
       </c>
       <c r="C85" t="n">
         <v>39.56000137329102</v>
@@ -2414,7 +2414,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>30.88977813720703</v>
+        <v>30.88978385925293</v>
       </c>
       <c r="C86" t="n">
         <v>42.15999984741211</v>
@@ -2443,7 +2443,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>30.75057601928711</v>
+        <v>30.75057411193848</v>
       </c>
       <c r="C87" t="n">
         <v>41.97000122070312</v>
@@ -2472,7 +2472,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>32.41375732421875</v>
+        <v>32.41375350952148</v>
       </c>
       <c r="C88" t="n">
         <v>44.2400016784668</v>
@@ -2501,7 +2501,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>34.18684387207031</v>
+        <v>34.18683624267578</v>
       </c>
       <c r="C89" t="n">
         <v>46.65999984741211</v>
@@ -2530,7 +2530,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>38.10032653808594</v>
+        <v>38.100341796875</v>
       </c>
       <c r="C90" t="n">
         <v>51.9900016784668</v>
@@ -2559,7 +2559,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>35.1543083190918</v>
+        <v>35.15433120727539</v>
       </c>
       <c r="C91" t="n">
         <v>47.97000122070312</v>
@@ -2588,7 +2588,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>38.21025848388672</v>
+        <v>38.21025466918945</v>
       </c>
       <c r="C92" t="n">
         <v>52.13999938964844</v>
@@ -2617,7 +2617,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>35.42494201660156</v>
+        <v>35.4249382019043</v>
       </c>
       <c r="C93" t="n">
         <v>48.33000183105469</v>
@@ -2646,7 +2646,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>35.55686950683594</v>
+        <v>35.55687713623047</v>
       </c>
       <c r="C94" t="n">
         <v>48.5099983215332</v>
@@ -2675,7 +2675,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>35.76193237304688</v>
+        <v>35.7619514465332</v>
       </c>
       <c r="C95" t="n">
         <v>48.77999877929688</v>
@@ -2704,7 +2704,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>38.79708480834961</v>
+        <v>38.79707336425781</v>
       </c>
       <c r="C96" t="n">
         <v>52.91999816894531</v>
@@ -2762,7 +2762,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>34.77945709228516</v>
+        <v>34.77945327758789</v>
       </c>
       <c r="C98" t="n">
         <v>47.43000030517578</v>
@@ -2820,7 +2820,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>34.90410614013672</v>
+        <v>34.90410995483398</v>
       </c>
       <c r="C100" t="n">
         <v>47.59999847412109</v>
@@ -2849,7 +2849,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>35.13142776489258</v>
+        <v>35.13142013549805</v>
       </c>
       <c r="C101" t="n">
         <v>47.90999984741211</v>
@@ -2907,7 +2907,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>34.54468536376953</v>
+        <v>34.544677734375</v>
       </c>
       <c r="C103" t="n">
         <v>47.09999847412109</v>
@@ -2936,7 +2936,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>35.87936401367188</v>
+        <v>35.87937545776367</v>
       </c>
       <c r="C104" t="n">
         <v>48.90999984741211</v>
@@ -2965,7 +2965,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>37.88938522338867</v>
+        <v>37.88938903808594</v>
       </c>
       <c r="C105" t="n">
         <v>51.65000152587891</v>
@@ -3023,7 +3023,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>39.27597427368164</v>
+        <v>39.27596664428711</v>
       </c>
       <c r="C107" t="n">
         <v>53.52999877929688</v>
@@ -3052,7 +3052,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>39.59880828857422</v>
+        <v>39.59880065917969</v>
       </c>
       <c r="C108" t="n">
         <v>53.97000122070312</v>
@@ -3081,7 +3081,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>39.70153427124023</v>
+        <v>39.70151901245117</v>
       </c>
       <c r="C109" t="n">
         <v>54.11000061035156</v>
@@ -3110,7 +3110,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>34.45541381835938</v>
+        <v>34.45540618896484</v>
       </c>
       <c r="C110" t="n">
         <v>46.95000076293945</v>
@@ -3139,7 +3139,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>38.46969985961914</v>
+        <v>38.46970367431641</v>
       </c>
       <c r="C111" t="n">
         <v>52.41999816894531</v>
@@ -3168,7 +3168,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>37.80920791625977</v>
+        <v>37.80922317504883</v>
       </c>
       <c r="C112" t="n">
         <v>51.52000045776367</v>
@@ -3197,7 +3197,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>39.13018798828125</v>
+        <v>39.13018417358398</v>
       </c>
       <c r="C113" t="n">
         <v>53.31999969482422</v>
@@ -3226,7 +3226,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>39.72554397583008</v>
+        <v>39.72555160522461</v>
       </c>
       <c r="C114" t="n">
         <v>54.08000183105469</v>
@@ -3255,7 +3255,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>40.57764434814453</v>
+        <v>40.57765960693359</v>
       </c>
       <c r="C115" t="n">
         <v>55.2400016784668</v>
@@ -3284,7 +3284,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>42.97943496704102</v>
+        <v>42.97944259643555</v>
       </c>
       <c r="C116" t="n">
         <v>58.45999908447266</v>
@@ -3342,7 +3342,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>36.47296524047852</v>
+        <v>36.47296905517578</v>
       </c>
       <c r="C118" t="n">
         <v>49.61000061035156</v>
@@ -3371,7 +3371,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>39.12599945068359</v>
+        <v>39.12599563598633</v>
       </c>
       <c r="C119" t="n">
         <v>53.16999816894531</v>
@@ -3400,7 +3400,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>39.80300903320312</v>
+        <v>39.80300521850586</v>
       </c>
       <c r="C120" t="n">
         <v>54.09000015258789</v>
@@ -3429,7 +3429,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>38.08106231689453</v>
+        <v>38.08107376098633</v>
       </c>
       <c r="C121" t="n">
         <v>51.75</v>
@@ -3458,7 +3458,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>31.37184906005859</v>
+        <v>31.37185668945312</v>
       </c>
       <c r="C122" t="n">
         <v>42.58000183105469</v>
@@ -3487,7 +3487,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>28.62368202209473</v>
+        <v>28.62368392944336</v>
       </c>
       <c r="C123" t="n">
         <v>38.84999847412109</v>
@@ -3516,7 +3516,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>30.76032829284668</v>
+        <v>30.76033020019531</v>
       </c>
       <c r="C124" t="n">
         <v>41.75</v>
@@ -3545,7 +3545,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>34.13397598266602</v>
+        <v>34.13398361206055</v>
       </c>
       <c r="C125" t="n">
         <v>46.27999877929688</v>
@@ -3574,7 +3574,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>34.34786224365234</v>
+        <v>34.34786987304688</v>
       </c>
       <c r="C126" t="n">
         <v>46.56999969482422</v>
@@ -3603,7 +3603,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>31.26488876342773</v>
+        <v>31.26489448547363</v>
       </c>
       <c r="C127" t="n">
         <v>42.38999938964844</v>
@@ -3632,7 +3632,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>32.42938613891602</v>
+        <v>32.42938232421875</v>
       </c>
       <c r="C128" t="n">
         <v>43.81000137329102</v>
@@ -3661,7 +3661,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>35.33845901489258</v>
+        <v>35.33845520019531</v>
       </c>
       <c r="C129" t="n">
         <v>47.7400016784668</v>
@@ -3690,7 +3690,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>34.96095275878906</v>
+        <v>34.96094512939453</v>
       </c>
       <c r="C130" t="n">
         <v>47.22999954223633</v>
@@ -3719,7 +3719,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>36.38218688964844</v>
+        <v>36.3822021484375</v>
       </c>
       <c r="C131" t="n">
         <v>49.15000152587891</v>
@@ -3748,7 +3748,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>41.87947845458984</v>
+        <v>41.87948226928711</v>
       </c>
       <c r="C132" t="n">
         <v>56.38999938964844</v>
@@ -3806,7 +3806,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>41.46358489990234</v>
+        <v>41.46359252929688</v>
       </c>
       <c r="C134" t="n">
         <v>55.83000183105469</v>
@@ -3835,7 +3835,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>44.54659271240234</v>
+        <v>44.54659652709961</v>
       </c>
       <c r="C135" t="n">
         <v>59.81000137329102</v>
@@ -3864,7 +3864,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>44.55403518676758</v>
+        <v>44.55405044555664</v>
       </c>
       <c r="C136" t="n">
         <v>59.81999969482422</v>
@@ -3893,7 +3893,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>44.15023040771484</v>
+        <v>44.15021896362305</v>
       </c>
       <c r="C137" t="n">
         <v>59.11999893188477</v>
@@ -3922,7 +3922,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>45.21065902709961</v>
+        <v>45.21066665649414</v>
       </c>
       <c r="C138" t="n">
         <v>60.54000091552734</v>
@@ -3980,7 +3980,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>51.11775970458984</v>
+        <v>51.11777496337891</v>
       </c>
       <c r="C140" t="n">
         <v>68.44999694824219</v>
@@ -4009,7 +4009,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>51.03940200805664</v>
+        <v>51.03939437866211</v>
       </c>
       <c r="C141" t="n">
         <v>68.02999877929688</v>
@@ -4038,7 +4038,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>54.57306289672852</v>
+        <v>54.57307052612305</v>
       </c>
       <c r="C142" t="n">
         <v>72.73999786376953</v>
@@ -4067,7 +4067,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>55.14325714111328</v>
+        <v>55.14326858520508</v>
       </c>
       <c r="C143" t="n">
         <v>73.5</v>
@@ -4096,7 +4096,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>56.88731002807617</v>
+        <v>56.88731384277344</v>
       </c>
       <c r="C144" t="n">
         <v>75.5</v>
@@ -4125,7 +4125,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>56.06603240966797</v>
+        <v>56.0660285949707</v>
       </c>
       <c r="C145" t="n">
         <v>74.41000366210938</v>
@@ -4154,7 +4154,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>59.13267135620117</v>
+        <v>59.13268280029297</v>
       </c>
       <c r="C146" t="n">
         <v>78.48000335693359</v>
@@ -4183,7 +4183,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>57.11053085327148</v>
+        <v>57.11052703857422</v>
       </c>
       <c r="C147" t="n">
         <v>75.48999786376953</v>
@@ -4210,7 +4210,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>51.06583786010742</v>
+        <v>51.06584548950195</v>
       </c>
       <c r="C148" t="n">
         <v>67.5</v>
@@ -4237,7 +4237,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>51.64836120605469</v>
+        <v>51.64837646484375</v>
       </c>
       <c r="C149" t="n">
         <v>68.26999664306641</v>
@@ -4264,7 +4264,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>50.69181060791016</v>
+        <v>50.69181823730469</v>
       </c>
       <c r="C150" t="n">
         <v>66.69000244140625</v>
@@ -4291,7 +4291,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>50.86664199829102</v>
+        <v>50.86664962768555</v>
       </c>
       <c r="C151" t="n">
         <v>66.91999816894531</v>
@@ -4318,7 +4318,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>54.64438629150391</v>
+        <v>54.6443977355957</v>
       </c>
       <c r="C152" t="n">
         <v>71.88999938964844</v>
@@ -4345,7 +4345,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>54.49165344238281</v>
+        <v>54.49166870117188</v>
       </c>
       <c r="C153" t="n">
         <v>71.23999786376953</v>
@@ -4372,7 +4372,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>54.87411117553711</v>
+        <v>54.87409591674805</v>
       </c>
       <c r="C154" t="n">
         <v>71.73999786376953</v>
@@ -4399,7 +4399,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>50.07051467895508</v>
+        <v>50.07051849365234</v>
       </c>
       <c r="C155" t="n">
         <v>65.45999908447266</v>
@@ -4426,7 +4426,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>49.89912796020508</v>
+        <v>49.89913177490234</v>
       </c>
       <c r="C156" t="n">
         <v>64.79000091552734</v>
@@ -4453,7 +4453,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>40.09490585327148</v>
+        <v>40.09490966796875</v>
       </c>
       <c r="C157" t="n">
         <v>52.06000137329102</v>
@@ -4480,7 +4480,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>49.64497756958008</v>
+        <v>49.64498519897461</v>
       </c>
       <c r="C158" t="n">
         <v>64.45999908447266</v>
@@ -4507,7 +4507,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>49.62170791625977</v>
+        <v>49.62171173095703</v>
       </c>
       <c r="C159" t="n">
         <v>63.97999954223633</v>
@@ -4536,7 +4536,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>48.25669479370117</v>
+        <v>48.25669097900391</v>
       </c>
       <c r="C160" t="n">
         <v>62.22000122070312</v>
@@ -4565,7 +4565,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>54.83361434936523</v>
+        <v>54.83361053466797</v>
       </c>
       <c r="C161" t="n">
         <v>70.69999694824219</v>
@@ -4594,7 +4594,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>48.51266479492188</v>
+        <v>48.51266860961914</v>
       </c>
       <c r="C162" t="n">
         <v>62.15000152587891</v>
@@ -4623,7 +4623,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>54.6635856628418</v>
+        <v>54.66357421875</v>
       </c>
       <c r="C163" t="n">
         <v>70.02999877929688</v>
@@ -4652,7 +4652,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>55.54563140869141</v>
+        <v>55.54565048217773</v>
       </c>
       <c r="C164" t="n">
         <v>71.16000366210938</v>
@@ -4681,7 +4681,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>50.60755157470703</v>
+        <v>50.60754013061523</v>
       </c>
       <c r="C165" t="n">
         <v>64.34999847412109</v>
@@ -4710,7 +4710,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>54.32740783691406</v>
+        <v>54.32741546630859</v>
       </c>
       <c r="C166" t="n">
         <v>69.08000183105469</v>
@@ -4739,7 +4739,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>56.51372528076172</v>
+        <v>56.51373291015625</v>
       </c>
       <c r="C167" t="n">
         <v>71.86000061035156</v>
@@ -4797,7 +4797,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>63.27793121337891</v>
+        <v>63.27793502807617</v>
       </c>
       <c r="C169" t="n">
         <v>79.88999938964844</v>
@@ -4826,7 +4826,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>59.32820892333984</v>
+        <v>59.32821273803711</v>
       </c>
       <c r="C170" t="n">
         <v>74.41000366210938</v>
@@ -4855,7 +4855,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>50.59760665893555</v>
+        <v>50.59760284423828</v>
       </c>
       <c r="C171" t="n">
         <v>63.45999908447266</v>
@@ -4884,7 +4884,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>33.58290481567383</v>
+        <v>33.58291625976562</v>
       </c>
       <c r="C172" t="n">
         <v>42.11999893188477</v>
@@ -4913,7 +4913,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>38.71762466430664</v>
+        <v>38.71762084960938</v>
       </c>
       <c r="C173" t="n">
         <v>48.56000137329102</v>
@@ -4942,7 +4942,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>38.60480499267578</v>
+        <v>38.60481262207031</v>
       </c>
       <c r="C174" t="n">
         <v>47.90999984741211</v>
@@ -4971,7 +4971,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>41.17522811889648</v>
+        <v>41.17523956298828</v>
       </c>
       <c r="C175" t="n">
         <v>51.09999847412109</v>
@@ -5000,7 +5000,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>40.70503234863281</v>
+        <v>40.70503997802734</v>
       </c>
       <c r="C176" t="n">
         <v>50.0099983215332</v>
@@ -5058,7 +5058,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>35.08885192871094</v>
+        <v>35.08885955810547</v>
       </c>
       <c r="C178" t="n">
         <v>43.11000061035156</v>
@@ -5116,7 +5116,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>45.37908935546875</v>
+        <v>45.37907791137695</v>
       </c>
       <c r="C180" t="n">
         <v>55.06999969482422</v>
@@ -5145,7 +5145,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>50.80941772460938</v>
+        <v>50.80941390991211</v>
       </c>
       <c r="C181" t="n">
         <v>61.65999984741211</v>
@@ -5174,7 +5174,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>48.19256591796875</v>
+        <v>48.19257736206055</v>
       </c>
       <c r="C182" t="n">
         <v>57.9900016784668</v>
@@ -5203,7 +5203,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>54.74955368041992</v>
+        <v>54.74954223632812</v>
       </c>
       <c r="C183" t="n">
         <v>65.87999725341797</v>
@@ -5232,7 +5232,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>60.4588508605957</v>
+        <v>60.45886611938477</v>
       </c>
       <c r="C184" t="n">
         <v>72.75</v>
@@ -5261,7 +5261,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>59.61572647094727</v>
+        <v>59.6157341003418</v>
       </c>
       <c r="C185" t="n">
         <v>71.23999786376953</v>
@@ -5319,7 +5319,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>59.2056770324707</v>
+        <v>59.20568466186523</v>
       </c>
       <c r="C187" t="n">
         <v>70.75</v>
@@ -5348,7 +5348,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>57.00894546508789</v>
+        <v>57.00895690917969</v>
       </c>
       <c r="C188" t="n">
         <v>67.62000274658203</v>
@@ -5377,7 +5377,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>60.6257438659668</v>
+        <v>60.62575149536133</v>
       </c>
       <c r="C189" t="n">
         <v>71.91000366210938</v>
@@ -5406,7 +5406,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>59.1672248840332</v>
+        <v>59.16722869873047</v>
       </c>
       <c r="C190" t="n">
         <v>70.18000030517578</v>
@@ -5435,7 +5435,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>58.7298698425293</v>
+        <v>58.72985458374023</v>
       </c>
       <c r="C191" t="n">
         <v>69.16000366210938</v>
@@ -5464,7 +5464,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>54.09328460693359</v>
+        <v>54.09328842163086</v>
       </c>
       <c r="C192" t="n">
         <v>63.70000076293945</v>
@@ -5493,7 +5493,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>51.28247451782227</v>
+        <v>51.28247833251953</v>
       </c>
       <c r="C193" t="n">
         <v>60.38999938964844</v>
@@ -5551,7 +5551,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>50.69358062744141</v>
+        <v>50.69358444213867</v>
       </c>
       <c r="C195" t="n">
         <v>59.22999954223633</v>
@@ -5609,7 +5609,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>41.68685913085938</v>
+        <v>41.68685150146484</v>
       </c>
       <c r="C197" t="n">
         <v>48.20999908447266</v>
@@ -5638,7 +5638,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>46.18326187133789</v>
+        <v>46.18326568603516</v>
       </c>
       <c r="C198" t="n">
         <v>53.40999984741211</v>
@@ -5667,7 +5667,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>39.76724624633789</v>
+        <v>39.76724243164062</v>
       </c>
       <c r="C199" t="n">
         <v>45.9900016784668</v>
@@ -5696,7 +5696,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>45.32010269165039</v>
+        <v>45.32010650634766</v>
       </c>
       <c r="C200" t="n">
         <v>51.90000152587891</v>
@@ -5725,7 +5725,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>42.62184906005859</v>
+        <v>42.62186431884766</v>
       </c>
       <c r="C201" t="n">
         <v>48.81000137329102</v>
@@ -5754,7 +5754,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>36.38705444335938</v>
+        <v>36.38705825805664</v>
       </c>
       <c r="C202" t="n">
         <v>41.66999816894531</v>
@@ -5812,7 +5812,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>42.76176834106445</v>
+        <v>42.76176071166992</v>
       </c>
       <c r="C204" t="n">
         <v>48.40999984741211</v>
@@ -5841,7 +5841,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>39.95278549194336</v>
+        <v>39.95279312133789</v>
       </c>
       <c r="C205" t="n">
         <v>45.22999954223633</v>
@@ -5928,7 +5928,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>41.82761001586914</v>
+        <v>41.82760620117188</v>
       </c>
       <c r="C208" t="n">
         <v>46.88999938964844</v>
@@ -5986,7 +5986,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>39.96850204467773</v>
+        <v>39.968505859375</v>
       </c>
       <c r="C210" t="n">
         <v>44.31999969482422</v>
@@ -6015,7 +6015,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>41.51963043212891</v>
+        <v>41.51963424682617</v>
       </c>
       <c r="C211" t="n">
         <v>46.04000091552734</v>
@@ -6044,7 +6044,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>42.98057556152344</v>
+        <v>42.98057174682617</v>
       </c>
       <c r="C212" t="n">
         <v>47.65999984741211</v>
@@ -6073,7 +6073,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>37.66802978515625</v>
+        <v>37.66803359985352</v>
       </c>
       <c r="C213" t="n">
         <v>41.29000091552734</v>
@@ -6102,7 +6102,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>37.52206802368164</v>
+        <v>37.52207183837891</v>
       </c>
       <c r="C214" t="n">
         <v>41.13000106811523</v>
@@ -6131,7 +6131,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>36.02592849731445</v>
+        <v>36.02592468261719</v>
       </c>
       <c r="C215" t="n">
         <v>39.4900016784668</v>
@@ -6160,7 +6160,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>42.60214614868164</v>
+        <v>42.60213851928711</v>
       </c>
       <c r="C216" t="n">
         <v>46.09999847412109</v>
@@ -6189,7 +6189,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>47.53697204589844</v>
+        <v>47.53696441650391</v>
       </c>
       <c r="C217" t="n">
         <v>51.43999862670898</v>
@@ -6218,7 +6218,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>51.90807723999023</v>
+        <v>51.90807342529297</v>
       </c>
       <c r="C218" t="n">
         <v>56.16999816894531</v>
@@ -6247,7 +6247,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>51.76910018920898</v>
+        <v>51.76910400390625</v>
       </c>
       <c r="C219" t="n">
         <v>55.4900016784668</v>
@@ -6305,7 +6305,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>57.21749877929688</v>
+        <v>57.21750259399414</v>
       </c>
       <c r="C221" t="n">
         <v>61.33000183105469</v>
@@ -6334,7 +6334,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>58.63678359985352</v>
+        <v>58.63678741455078</v>
       </c>
       <c r="C222" t="n">
         <v>62.31000137329102</v>
@@ -6421,7 +6421,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>59.5145263671875</v>
+        <v>59.51452255249023</v>
       </c>
       <c r="C225" t="n">
         <v>62.63999938964844</v>
@@ -6450,7 +6450,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>59.47651672363281</v>
+        <v>59.47651290893555</v>
       </c>
       <c r="C226" t="n">
         <v>62.59999847412109</v>
@@ -6537,7 +6537,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>67.47087860107422</v>
+        <v>67.47088623046875</v>
       </c>
       <c r="C229" t="n">
         <v>70.38999938964844</v>
@@ -6566,7 +6566,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>78.05304718017578</v>
+        <v>78.05306243896484</v>
       </c>
       <c r="C230" t="n">
         <v>81.43000030517578</v>
@@ -6595,7 +6595,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>77.16510009765625</v>
+        <v>77.16509246826172</v>
       </c>
       <c r="C231" t="n">
         <v>79.94999694824219</v>
@@ -6624,7 +6624,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>68.51719665527344</v>
+        <v>68.51720428466797</v>
       </c>
       <c r="C232" t="n">
         <v>70.98999786376953</v>
@@ -6682,7 +6682,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>73.27769470214844</v>
+        <v>73.27768707275391</v>
       </c>
       <c r="C234" t="n">
         <v>75.31999969482422</v>
@@ -6711,7 +6711,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>82.81197357177734</v>
+        <v>82.81198120117188</v>
       </c>
       <c r="C235" t="n">
         <v>85.12000274658203</v>
@@ -6856,7 +6856,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>102.0586700439453</v>
+        <v>102.0586776733398</v>
       </c>
       <c r="C240" t="n">
         <v>103.5999984741211</v>
@@ -6885,7 +6885,7 @@
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>114.9539184570312</v>
+        <v>114.9539260864258</v>
       </c>
       <c r="C241" t="n">
         <v>116.6900024414062</v>
